--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.59774</v>
+        <v>16.68912</v>
       </c>
       <c r="D2" t="n">
-        <v>16.91022</v>
+        <v>16.20587</v>
       </c>
       <c r="E2" t="n">
-        <v>16.49757</v>
+        <v>16.5004</v>
       </c>
       <c r="F2" t="n">
-        <v>42.14252</v>
+        <v>42.12669</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05018</v>
+        <v>0.05023</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82424</v>
+        <v>1.80468</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.61751</v>
+        <v>17.05355</v>
       </c>
       <c r="D3" t="n">
-        <v>16.39972</v>
+        <v>16.273</v>
       </c>
       <c r="E3" t="n">
-        <v>16.72646</v>
+        <v>16.5386</v>
       </c>
       <c r="F3" t="n">
-        <v>42.69182</v>
+        <v>43.17688</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05072</v>
+        <v>0.0493</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80011</v>
+        <v>1.81526</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.49285</v>
+        <v>16.66397</v>
       </c>
       <c r="D4" t="n">
-        <v>16.26732</v>
+        <v>16.1267</v>
       </c>
       <c r="E4" t="n">
-        <v>16.66455</v>
+        <v>16.58827</v>
       </c>
       <c r="F4" t="n">
-        <v>42.98191</v>
+        <v>42.07992</v>
       </c>
       <c r="G4" t="n">
         <v>0.05037</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82367</v>
+        <v>1.79909</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.58282</v>
+        <v>16.69117</v>
       </c>
       <c r="D6" t="n">
-        <v>15.7141</v>
+        <v>15.87091</v>
       </c>
       <c r="E6" t="n">
-        <v>16.49253</v>
+        <v>16.18954</v>
       </c>
       <c r="F6" t="n">
-        <v>21.36303</v>
+        <v>21.22825</v>
       </c>
       <c r="G6" t="n">
-        <v>34.05328</v>
+        <v>34.03547</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.43341</v>
+        <v>16.53484</v>
       </c>
       <c r="D7" t="n">
-        <v>16.23098</v>
+        <v>16.09734</v>
       </c>
       <c r="E7" t="n">
-        <v>16.15861</v>
+        <v>16.19644</v>
       </c>
       <c r="F7" t="n">
-        <v>21.45969</v>
+        <v>21.15755</v>
       </c>
       <c r="G7" t="n">
-        <v>33.71515</v>
+        <v>34.06294</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.55722</v>
+        <v>16.81379</v>
       </c>
       <c r="D8" t="n">
-        <v>16.02813</v>
+        <v>15.99714</v>
       </c>
       <c r="E8" t="n">
-        <v>16.31365</v>
+        <v>16.16477</v>
       </c>
       <c r="F8" t="n">
-        <v>21.25232</v>
+        <v>21.86303</v>
       </c>
       <c r="G8" t="n">
-        <v>34.54555</v>
+        <v>34.26954</v>
       </c>
     </row>
   </sheetData>
